--- a/examples/horoscopes.xlsx
+++ b/examples/horoscopes.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -28,7 +28,7 @@
     <t xml:space="preserve">Знак</t>
   </si>
   <si>
-    <t xml:space="preserve">Гороскоп</t>
+    <t xml:space="preserve">Текст</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-05</t>
@@ -57,6 +57,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -78,11 +79,13 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -132,23 +135,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -289,7 +292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -300,7 +303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
